--- a/erp-server/erp-server-file/src/main/resources/excel/wms/sampleTransferInfoExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/sampleTransferInfoExport.xlsx
@@ -1,35 +1,48 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <bookViews>
-    <workbookView windowWidth="24945" windowHeight="17655"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel</Application>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>工作表</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>3</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="3" baseType="lpstr">
+      <vt:lpstr>Sheet1</vt:lpstr>
+      <vt:lpstr>Sheet2</vt:lpstr>
+      <vt:lpstr>Sheet3</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <cp:lastModifiedBy>Administrator</cp:lastModifiedBy>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2006-09-16T00:00:00Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2025-10-31T02:43:05Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="2" name="ICV">
+    <vt:lpwstr>7F7DFA33A32D4A58938CE18BC6603B26_12</vt:lpwstr>
+  </property>
+  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="3" name="KSOProductBuildVer">
+    <vt:lpwstr>2052-12.1.0.23125</vt:lpwstr>
+  </property>
+</Properties>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>样品转移单号</t>
   </si>
@@ -37,18 +50,33 @@
     <t>单据状态</t>
   </si>
   <si>
+    <t>转移类型</t>
+  </si>
+  <si>
     <t>作废状态</t>
   </si>
   <si>
     <t>转移日期</t>
   </si>
   <si>
+    <t>转入人</t>
+  </si>
+  <si>
+    <t>转出人</t>
+  </si>
+  <si>
     <t>SKU</t>
   </si>
   <si>
     <t>产品名称</t>
   </si>
   <si>
+    <t>原使用方</t>
+  </si>
+  <si>
+    <t>目标使用方</t>
+  </si>
+  <si>
     <t>转移数量</t>
   </si>
   <si>
@@ -61,12 +89,6 @@
     <t>审核完成时间</t>
   </si>
   <si>
-    <t>转入人</t>
-  </si>
-  <si>
-    <t>转出人</t>
-  </si>
-  <si>
     <t>创建人</t>
   </si>
   <si>
@@ -79,18 +101,33 @@
     <t>{.approveStatusName}</t>
   </si>
   <si>
+    <t>{.transferTypeName}</t>
+  </si>
+  <si>
     <t>{.invalidStatusName}</t>
   </si>
   <si>
     <t>{.transferDate}</t>
   </si>
   <si>
+    <t>{.transferInUserName}</t>
+  </si>
+  <si>
+    <t>{.transferOutUserName}</t>
+  </si>
+  <si>
     <t>{.skuNo}</t>
   </si>
   <si>
     <t>{.productName}</t>
   </si>
   <si>
+    <t>{.useUserName}</t>
+  </si>
+  <si>
+    <t>{.targetUseUserName}</t>
+  </si>
+  <si>
     <t>{.transferQty}</t>
   </si>
   <si>
@@ -101,12 +138,6 @@
   </si>
   <si>
     <t>{.approveTime}</t>
-  </si>
-  <si>
-    <t>{.transferInUserName}</t>
-  </si>
-  <si>
-    <t>{.transferOutUserName}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -117,7 +148,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
@@ -789,7 +820,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -1073,28 +1104,56 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="24945" windowHeight="17655"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="17.625" customWidth="1"/>
-    <col min="2" max="2" width="22.25" customWidth="1"/>
-    <col min="3" max="4" width="17.125" customWidth="1"/>
-    <col min="5" max="5" width="15.625" customWidth="1"/>
-    <col min="6" max="6" width="24.625" customWidth="1"/>
-    <col min="7" max="7" width="17.875" customWidth="1"/>
-    <col min="8" max="8" width="15.75" customWidth="1"/>
+    <col min="2" max="3" width="17.125" customWidth="1"/>
+    <col min="4" max="4" width="15.625" customWidth="1"/>
+    <col min="5" max="5" width="17.125" customWidth="1"/>
+    <col min="6" max="7" width="15.625" customWidth="1"/>
+    <col min="8" max="8" width="17.875" customWidth="1"/>
     <col min="9" max="9" width="18.75" customWidth="1"/>
-    <col min="10" max="10" width="17.625" customWidth="1"/>
-    <col min="11" max="11" width="15.25" customWidth="1"/>
-    <col min="12" max="13" width="19.25" customWidth="1"/>
-    <col min="14" max="14" width="15.5" customWidth="1"/>
-    <col min="15" max="15" width="8.875" customWidth="1"/>
+    <col min="10" max="11" width="17.625" customWidth="1"/>
+    <col min="12" max="12" width="15.25" customWidth="1"/>
+    <col min="13" max="13" width="19.25" customWidth="1"/>
+    <col min="14" max="15" width="17.625" customWidth="1"/>
+    <col min="16" max="17" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:14">
+    <row r="1" customFormat="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1137,49 +1196,67 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="N2" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1189,7 +1266,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
@@ -1200,7 +1277,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
